--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104668_W24.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104668_W24.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7611</v>
+        <v>7.8085</v>
       </c>
       <c r="E2" t="n">
-        <v>6.584</v>
+        <v>6.9859</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1771</v>
+        <v>0.8226</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2984</v>
+        <v>3.2983</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3419</v>
+        <v>1.344</v>
       </c>
       <c r="I2" t="n">
-        <v>1.9565</v>
+        <v>1.9543</v>
       </c>
       <c r="J2" t="n">
-        <v>4.184</v>
+        <v>4.1406</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2889</v>
+        <v>2.2645</v>
       </c>
       <c r="L2" t="n">
-        <v>1.895</v>
+        <v>1.8761</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8856000000000001</v>
+        <v>-0.8423</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.947</v>
+        <v>-0.9205</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0614</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2955</v>
+        <v>-0.2331</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9557</v>
+        <v>-0.4835</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6602</v>
+        <v>0.2504</v>
       </c>
       <c r="V2" t="n">
-        <v>4.5314</v>
+        <v>4.5157</v>
       </c>
       <c r="W2" t="n">
-        <v>5.6241</v>
+        <v>5.6051</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5865</v>
+        <v>3.4191</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4896</v>
+        <v>2.5781</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0969</v>
+        <v>0.841</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9065</v>
+        <v>0.9125</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8772</v>
+        <v>0.8842</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0293</v>
+        <v>0.0283</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4304</v>
+        <v>1.4132</v>
       </c>
       <c r="K3" t="n">
-        <v>1.697</v>
+        <v>1.6892</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2666</v>
+        <v>-0.276</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5239</v>
+        <v>-0.5007</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8198</v>
+        <v>-0.805</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0517</v>
+        <v>-0.217</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5383</v>
+        <v>-0.4207</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4866</v>
+        <v>0.2036</v>
       </c>
       <c r="V3" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="W3" t="n">
-        <v>2.7317</v>
+        <v>2.7237</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3809</v>
+        <v>1.568</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7834</v>
+        <v>2.0002</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4025</v>
+        <v>-0.4323</v>
       </c>
       <c r="G4" t="n">
-        <v>0.462</v>
+        <v>0.4755</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.6119</v>
+        <v>-1.6058</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0738</v>
+        <v>2.0813</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6626</v>
+        <v>1.6513</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3565</v>
+        <v>0.348</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3061</v>
+        <v>1.3033</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2007</v>
+        <v>-1.1758</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.9684</v>
+        <v>-1.9538</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7678</v>
+        <v>0.778</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0097</v>
+        <v>0.1835</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.747</v>
+        <v>-0.5113</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7567</v>
+        <v>0.6948</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1938</v>
+        <v>1.0098</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1571</v>
+        <v>0.9154</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0368</v>
+        <v>0.0944</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0421</v>
+        <v>3.0501</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5698</v>
+        <v>3.5727</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5276999999999999</v>
+        <v>-0.5226</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1955</v>
+        <v>3.1756</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2729</v>
+        <v>3.2578</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1534</v>
+        <v>-0.1255</v>
       </c>
       <c r="N5" t="n">
-        <v>0.297</v>
+        <v>0.3149</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R5" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9409</v>
+        <v>-1.1297</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2299</v>
+        <v>0.0161</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1708</v>
+        <v>-1.1458</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9009</v>
+        <v>0.489</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9851</v>
+        <v>1.2496</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0842</v>
+        <v>-0.7607</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7255</v>
+        <v>-0.712</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1195</v>
+        <v>0.1342</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.845</v>
+        <v>-0.8462</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4938</v>
+        <v>0.4754</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9871</v>
+        <v>0.9825</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4932</v>
+        <v>-0.5071</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2193</v>
+        <v>-1.1874</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8675</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1727</v>
+        <v>-0.2543</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8257</v>
+        <v>0.1204</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.653</v>
+        <v>-0.3747</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7997</v>
+        <v>1.792</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E. DURAN</t>
+          <t>J. JOHNSON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1732</v>
+        <v>-0.1568</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-0.4229</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1732</v>
+        <v>0.2661</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0159</v>
+        <v>-0.1372</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1732</v>
+        <v>0.1491</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1573</v>
+        <v>-0.2863</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0.3532</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.0345</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.3877</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0159</v>
+        <v>0.216</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1732</v>
+        <v>0.1146</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1573</v>
+        <v>0.1014</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1573</v>
+        <v>-0.2473</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.0697</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1573</v>
+        <v>-0.1775</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. JOHNSON</t>
+          <t>E. DURAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2624</v>
+        <v>-0.1724</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5526</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2902</v>
+        <v>-0.1724</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1357</v>
+        <v>-0.0144</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1442</v>
+        <v>-0.1724</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2799</v>
+        <v>0.1579</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3439</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0346</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3786</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2082</v>
+        <v>-0.0144</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1096</v>
+        <v>-0.1724</v>
       </c>
       <c r="O8" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.1579</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2268</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3536</v>
+        <v>-0.1579</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2087</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1449</v>
+        <v>-0.1579</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. NGOUAMA</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9727</v>
+        <v>-1.0621</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5384</v>
+        <v>0.4819</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5657</v>
+        <v>-1.5439</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2762</v>
+        <v>0.6241</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4735</v>
+        <v>0.5227000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1973</v>
+        <v>0.1014</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.48</v>
+        <v>0.5516</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.44</v>
+        <v>0.5516</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2038</v>
+        <v>0.0725</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0335</v>
+        <v>-0.0289</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2373</v>
+        <v>0.1014</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1342</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3185</v>
+        <v>-0.4389</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0907</v>
+        <v>-0.0697</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2277</v>
+        <v>-0.3692</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>M. NGOUAMA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2712</v>
+        <v>-1.2781</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3455</v>
+        <v>-2.7804</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.6166</v>
+        <v>1.5023</v>
       </c>
       <c r="G10" t="n">
-        <v>0.621</v>
+        <v>-0.2574</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5223</v>
+        <v>-0.4603</v>
       </c>
       <c r="I10" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.2028</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5541</v>
+        <v>-0.4898</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5541</v>
+        <v>-0.4449</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.0449</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0669</v>
+        <v>0.2324</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0318</v>
+        <v>-0.0154</v>
       </c>
       <c r="O10" t="n">
-        <v>0.09859999999999999</v>
+        <v>0.2477</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6388</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2087</v>
+        <v>-0.1233</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4301</v>
+        <v>0.1317</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4276</v>
+        <v>-2.8685</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.121</v>
+        <v>-0.8176</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.3065</v>
+        <v>-2.0509</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6877</v>
+        <v>-1.6872</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.5512</v>
+        <v>-2.545</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8636</v>
+        <v>0.8578</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.2711</v>
+        <v>-0.297</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.8974</v>
+        <v>-0.907</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6263</v>
+        <v>0.61</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4166</v>
+        <v>-1.3902</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6539</v>
+        <v>-1.638</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2373</v>
+        <v>0.2477</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9518</v>
+        <v>-0.3798</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8861</v>
+        <v>-0.5323</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.06560000000000001</v>
+        <v>0.1524</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W11" t="n">
-        <v>3.4387</v>
+        <v>3.4262</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.9243</v>
+        <v>-3.2612</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1059</v>
+        <v>-1.7624</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8183</v>
+        <v>-1.4988</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.3272</v>
+        <v>-0.3197</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.042</v>
+        <v>-0.0321</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2852</v>
+        <v>-0.2876</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3042</v>
+        <v>-0.3245</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3708</v>
+        <v>-0.376</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0665</v>
+        <v>0.0515</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.023</v>
+        <v>0.0048</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3288</v>
+        <v>0.3438</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3517</v>
+        <v>-0.3391</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6631</v>
+        <v>-1.0113</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6261</v>
+        <v>-0.251</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0371</v>
+        <v>-0.7603</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.791799999999999</v>
+        <v>5.495299999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>8.026799999999998</v>
+        <v>8.4278</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.2346</v>
+        <v>-2.9326</v>
       </c>
       <c r="G13" t="n">
-        <v>5.1618</v>
+        <v>5.232600000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7231</v>
+        <v>1.7913</v>
       </c>
       <c r="I13" t="n">
-        <v>3.4386</v>
+        <v>3.4411</v>
       </c>
       <c r="J13" t="n">
-        <v>10.1212</v>
+        <v>9.943199999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>7.482899999999999</v>
+        <v>7.400199999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>2.6382</v>
+        <v>2.5431</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.9595</v>
+        <v>-4.710599999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-5.7597</v>
+        <v>-5.609</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8004000000000001</v>
+        <v>0.8979000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q13" t="n">
-        <v>-15.8783</v>
+        <v>-15.9343</v>
       </c>
       <c r="R13" t="n">
-        <v>12.4759</v>
+        <v>12.5198</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.5518</v>
+        <v>-3.8774</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.0243</v>
+        <v>-2.325</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5276</v>
+        <v>-1.5525</v>
       </c>
       <c r="V13" t="n">
-        <v>7.584499999999999</v>
+        <v>7.554900000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>16.8081</v>
+        <v>16.744</v>
       </c>
       <c r="X13" t="n">
-        <v>-9.223599999999999</v>
+        <v>-9.189</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.6122</v>
+        <v>5.5368</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1125</v>
+        <v>4.2753</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4997</v>
+        <v>1.2615</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2472</v>
+        <v>1.2227</v>
       </c>
       <c r="H14" t="n">
-        <v>3.1372</v>
+        <v>3.1255</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.89</v>
+        <v>-1.9028</v>
       </c>
       <c r="J14" t="n">
-        <v>2.2456</v>
+        <v>2.1944</v>
       </c>
       <c r="K14" t="n">
-        <v>3.9411</v>
+        <v>3.916</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.6955</v>
+        <v>-1.7217</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.9984</v>
+        <v>-0.9717</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.7906</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9962</v>
+        <v>0.9546</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1693</v>
+        <v>0.0692</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1656</v>
+        <v>0.8854</v>
       </c>
       <c r="V14" t="n">
-        <v>4.0492</v>
+        <v>4.0424</v>
       </c>
       <c r="W14" t="n">
-        <v>4.5314</v>
+        <v>4.5157</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.4822</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5536</v>
+        <v>3.5291</v>
       </c>
       <c r="E15" t="n">
-        <v>3.244</v>
+        <v>2.1475</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3096</v>
+        <v>1.3816</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1625</v>
+        <v>-0.1606</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.6796</v>
+        <v>-0.6806</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5171</v>
+        <v>0.52</v>
       </c>
       <c r="J15" t="n">
-        <v>1.225</v>
+        <v>1.1979</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2975</v>
+        <v>0.2823</v>
       </c>
       <c r="L15" t="n">
-        <v>0.9275</v>
+        <v>0.9156</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3875</v>
+        <v>-1.3585</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9771</v>
+        <v>-0.9629</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4104</v>
+        <v>-0.3956</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7161</v>
+        <v>0.6897</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1947</v>
+        <v>0.1365</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5214</v>
+        <v>0.5532</v>
       </c>
       <c r="V15" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4162</v>
+        <v>2.2485</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0651</v>
+        <v>1.8093</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3511</v>
+        <v>0.4391</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0997</v>
+        <v>0.0999</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4948</v>
+        <v>-0.5022</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5945</v>
+        <v>0.6021</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0904</v>
+        <v>1.0732</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4187</v>
+        <v>0.403</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6717</v>
+        <v>0.6703</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9908</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9135</v>
+        <v>-0.9052</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0772</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0445</v>
+        <v>-0.2173</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1179</v>
+        <v>-0.3534</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0735</v>
+        <v>0.1361</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DIAGNE</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1837</v>
+        <v>1.6962</v>
       </c>
       <c r="E17" t="n">
-        <v>1.13</v>
+        <v>2.7682</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0537</v>
+        <v>-1.072</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0214</v>
+        <v>1.9323</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1732</v>
+        <v>-0.0489</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1946</v>
+        <v>1.9812</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0373</v>
+        <v>2.9637</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.655</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0373</v>
+        <v>2.3087</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0159</v>
+        <v>-1.0314</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1732</v>
+        <v>-0.7039</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1573</v>
+        <v>-0.3275</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0696</v>
+        <v>-0.0572</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-0.1955</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0696</v>
+        <v>0.1383</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>A. DIAGNE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8848</v>
+        <v>1.4189</v>
       </c>
       <c r="E18" t="n">
-        <v>2.0674</v>
+        <v>1.3636</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1826</v>
+        <v>0.0553</v>
       </c>
       <c r="G18" t="n">
-        <v>1.93</v>
+        <v>0.0228</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0505</v>
+        <v>-0.1724</v>
       </c>
       <c r="I18" t="n">
-        <v>1.9805</v>
+        <v>0.1952</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9717</v>
+        <v>0.0372</v>
       </c>
       <c r="K18" t="n">
-        <v>0.658</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2.3136</v>
+        <v>0.0372</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0417</v>
+        <v>-0.0144</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7086</v>
+        <v>-0.1724</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3331</v>
+        <v>0.1579</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8598</v>
+        <v>0.3066</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9043</v>
+        <v>0.2369</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0445</v>
+        <v>0.0697</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. GOLOMAN</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3054</v>
+        <v>-0.923</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2107</v>
+        <v>0.8698</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0946</v>
+        <v>-1.7927</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.494</v>
+        <v>0.246</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.0863</v>
+        <v>0.7095</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4078</v>
+        <v>-0.4635</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0364</v>
+        <v>0.2733</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.7081</v>
+        <v>1.4134</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6717</v>
+        <v>-1.1401</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4576</v>
+        <v>-0.0273</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3781</v>
+        <v>-0.7039</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0795</v>
+        <v>0.6766</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.361</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5762</v>
+        <v>0.5759</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1867</v>
+        <v>0.4387</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3895</v>
+        <v>0.1372</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.1607</v>
+        <v>-3.1107</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.1607</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>G. GOLOMAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.236</v>
+        <v>-1.5418</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7706</v>
+        <v>-1.5295</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0067</v>
+        <v>-0.0124</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2529</v>
+        <v>-2.5035</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7114</v>
+        <v>-2.1015</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4585</v>
+        <v>-0.4019</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2924</v>
+        <v>-1.0576</v>
       </c>
       <c r="K20" t="n">
-        <v>1.42</v>
+        <v>-1.7279</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.1276</v>
+        <v>0.6703</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0395</v>
+        <v>-1.4458</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7086</v>
+        <v>-0.3736</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6691</v>
+        <v>-1.0722</v>
       </c>
       <c r="P20" t="n">
-        <v>1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2674</v>
+        <v>1.347</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3176</v>
+        <v>0.894</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0502</v>
+        <v>0.4531</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.1173</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.278</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6481</v>
+        <v>-3.2949</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3679</v>
+        <v>-2.0956</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2802</v>
+        <v>-1.1993</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.4976</v>
+        <v>-3.5117</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.88</v>
+        <v>-0.8898</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.6176</v>
+        <v>-2.6219</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.4718</v>
+        <v>-2.4948</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1874</v>
+        <v>-0.2003</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.2844</v>
+        <v>-2.2945</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0258</v>
+        <v>-1.0169</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6927</v>
+        <v>-0.6895</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1275</v>
+        <v>0.4852</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1039</v>
+        <v>0.3992</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0236</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.7455</v>
+        <v>-3.7024</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8616</v>
+        <v>-1.3077</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.8839</v>
+        <v>-2.3947</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3478</v>
+        <v>0.3475</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4265</v>
+        <v>-0.4276</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4501</v>
+        <v>1.422</v>
       </c>
       <c r="K22" t="n">
-        <v>1.309</v>
+        <v>1.296</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1411</v>
+        <v>0.1259</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5289</v>
+        <v>-1.502</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.9485</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0673</v>
+        <v>-0.0384</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8166</v>
+        <v>-0.2257</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2507</v>
+        <v>0.1873</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.5994</v>
+        <v>-3.584</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-3.5994</v>
+        <v>-3.584</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.917</v>
+        <v>-4.3543</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3829</v>
+        <v>-2.8072</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.5342</v>
+        <v>-1.5471</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.1362</v>
+        <v>-2.1391</v>
       </c>
       <c r="H23" t="n">
         <v>-1.2005</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9356</v>
+        <v>-0.9386</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.6408</v>
+        <v>-1.6525</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6651</v>
+        <v>-0.669</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.9756</v>
+        <v>-0.9835</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4954</v>
+        <v>-0.4866</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5354</v>
+        <v>-0.5315</v>
       </c>
       <c r="O23" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1418</v>
+        <v>0.4191</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6079</v>
+        <v>-0.0166</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4661</v>
+        <v>0.4356</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5904</v>
+        <v>-4.6217</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.332</v>
+        <v>-2.5612</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2584</v>
+        <v>-2.0605</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3439</v>
+        <v>-0.3612</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3546</v>
+        <v>-0.3778</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0107</v>
+        <v>0.0166</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7959000000000001</v>
+        <v>0.754</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2762</v>
+        <v>0.2403</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1398</v>
+        <v>-1.1152</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6308</v>
+        <v>-0.6182</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.0877</v>
+        <v>0.8988</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6593</v>
+        <v>0.1691</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5716</v>
+        <v>0.7297</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.1173</v>
+        <v>-3.1107</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.278</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.791899999999999</v>
+        <v>-4.008600000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>3.234500000000001</v>
+        <v>2.932499999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.0265</v>
+        <v>-6.941199999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.1617</v>
+        <v>-5.232400000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.7231</v>
+        <v>-1.7912</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.4386</v>
+        <v>-3.4412</v>
       </c>
       <c r="J25" t="n">
-        <v>4.959399999999999</v>
+        <v>4.710799999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>5.759900000000001</v>
+        <v>5.6088</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.8004999999999998</v>
+        <v>-0.8982</v>
       </c>
       <c r="M25" t="n">
-        <v>-10.1213</v>
+        <v>-9.943099999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.4831</v>
+        <v>-7.4002</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.638</v>
+        <v>-2.5431</v>
       </c>
       <c r="P25" t="n">
-        <v>3.402500000000001</v>
+        <v>3.414499999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-12.4759</v>
+        <v>-12.5197</v>
       </c>
       <c r="R25" t="n">
-        <v>15.8784</v>
+        <v>15.9343</v>
       </c>
       <c r="S25" t="n">
-        <v>4.5519</v>
+        <v>5.364000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>1.527600000000001</v>
+        <v>1.5524</v>
       </c>
       <c r="U25" t="n">
-        <v>3.0245</v>
+        <v>3.8116</v>
       </c>
       <c r="V25" t="n">
-        <v>-7.5845</v>
+        <v>-7.555</v>
       </c>
       <c r="W25" t="n">
-        <v>9.2235</v>
+        <v>9.1892</v>
       </c>
       <c r="X25" t="n">
-        <v>-16.8079</v>
+        <v>-16.7439</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104668_W24.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104668_W24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-9.189</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-3.584</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104668_W24.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-16.7439</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
